--- a/diseases/d059/2010-2014.xlsx
+++ b/diseases/d059/2010-2014.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1309,9 +1306,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1605,9 +1599,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -1901,9 +1892,6 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -2197,9 +2185,6 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -2493,9 +2478,6 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
@@ -2789,9 +2771,6 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -3085,9 +3064,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -3381,9 +3357,6 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -3677,9 +3650,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -3973,9 +3943,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -4269,9 +4236,6 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -4565,9 +4529,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -4861,9 +4822,6 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
@@ -5257,9 +5215,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -5553,9 +5508,6 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
@@ -5849,9 +5801,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -6145,9 +6094,6 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -6441,9 +6387,6 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
@@ -6737,9 +6680,6 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
@@ -7033,9 +6973,6 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -7329,9 +7266,6 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
@@ -7625,9 +7559,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -7921,9 +7852,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -8217,9 +8145,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -8513,9 +8438,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -8809,9 +8731,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -9205,9 +9124,6 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -9501,9 +9417,6 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
@@ -9797,9 +9710,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -10093,9 +10003,6 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -10389,9 +10296,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -10685,9 +10589,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -10981,9 +10882,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -11277,9 +11175,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -11573,9 +11468,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -12313,9 +12205,6 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
@@ -13201,9 +13090,6 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
@@ -14237,9 +14123,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -15273,9 +15156,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -15669,9 +15549,6 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
@@ -16705,9 +16582,6 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
@@ -17593,9 +17467,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -18481,9 +18352,6 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -19369,9 +19237,6 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
@@ -20405,9 +20270,6 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
@@ -21293,9 +21155,6 @@
       <c r="O138" t="n">
         <v>0</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0</v>
       </c>
@@ -22181,9 +22040,6 @@
       <c r="O144" t="n">
         <v>0</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0</v>
       </c>
@@ -23217,9 +23073,6 @@
       <c r="O151" t="n">
         <v>0</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0</v>
       </c>
@@ -24105,9 +23958,6 @@
       <c r="O157" t="n">
         <v>0</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0</v>
       </c>
@@ -25141,9 +24991,6 @@
       <c r="O164" t="n">
         <v>0</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0</v>
       </c>
@@ -26029,9 +25876,6 @@
       <c r="O170" t="n">
         <v>0</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0</v>
       </c>
@@ -27065,9 +26909,6 @@
       <c r="O177" t="n">
         <v>0</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>0</v>
       </c>
@@ -27461,9 +27302,6 @@
       <c r="O179" t="n">
         <v>0</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0</v>
       </c>
@@ -28497,9 +28335,6 @@
       <c r="O186" t="n">
         <v>0</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0</v>
       </c>
@@ -29385,9 +29220,6 @@
       <c r="O192" t="n">
         <v>0</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0</v>
       </c>
@@ -30273,9 +30105,6 @@
       <c r="O198" t="n">
         <v>0</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0</v>
       </c>
@@ -31161,9 +30990,6 @@
       <c r="O204" t="n">
         <v>0</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>0</v>
       </c>
@@ -32197,9 +32023,6 @@
       <c r="O211" t="n">
         <v>0</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="R211" t="n">
         <v>0</v>
       </c>
@@ -33085,9 +32908,6 @@
       <c r="O217" t="n">
         <v>0</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="R217" t="n">
         <v>0</v>
       </c>
@@ -34121,9 +33941,6 @@
       <c r="O224" t="n">
         <v>0</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0</v>
       </c>
@@ -35009,9 +34826,6 @@
       <c r="O230" t="n">
         <v>0</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>0</v>
       </c>
@@ -35897,9 +35711,6 @@
       <c r="O236" t="n">
         <v>0</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0</v>
       </c>
@@ -36933,9 +36744,6 @@
       <c r="O243" t="n">
         <v>0</v>
       </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
       <c r="R243" t="n">
         <v>0</v>
       </c>
@@ -37819,9 +37627,6 @@
         <v>0</v>
       </c>
       <c r="O249" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q249" t="n">
         <v>0</v>
       </c>
       <c r="R249" t="n">
